--- a/results/05-2026/no_obbba_medicaid/beta/inputs-05-2026.xlsx
+++ b/results/05-2026/no_obbba_medicaid/beta/inputs-05-2026.xlsx
@@ -4494,7 +4494,7 @@
         <v>0.7</v>
       </c>
       <c r="AH25" t="n">
-        <v>1069</v>
+        <v>1993.526</v>
       </c>
       <c r="AI25" t="n">
         <v>344.974</v>
@@ -4545,7 +4545,7 @@
         <v>0.315</v>
       </c>
       <c r="AY25" t="n">
-        <v>1506.358125</v>
+        <v>1714.376475</v>
       </c>
       <c r="AZ25" t="n">
         <v>298.541025</v>
@@ -4652,7 +4652,7 @@
         <v>0.7</v>
       </c>
       <c r="AH26" t="n">
-        <v>1073</v>
+        <v>2031.324</v>
       </c>
       <c r="AI26" t="n">
         <v>342.676</v>
@@ -4703,7 +4703,7 @@
         <v>0.315</v>
       </c>
       <c r="AY26" t="n">
-        <v>1340.233425</v>
+        <v>1763.874675</v>
       </c>
       <c r="AZ26" t="n">
         <v>304.437825</v>
@@ -4861,7 +4861,7 @@
         <v>0.28035</v>
       </c>
       <c r="AY27" t="n">
-        <v>1380.6397775739</v>
+        <v>1804.2810275739</v>
       </c>
       <c r="AZ27" t="n">
         <v>311.872410869757</v>
@@ -5019,7 +5019,7 @@
         <v>0.250425</v>
       </c>
       <c r="AY28" t="n">
-        <v>1417.76026403992</v>
+        <v>1841.40151403992</v>
       </c>
       <c r="AZ28" t="n">
         <v>314.478800818207</v>
@@ -5177,7 +5177,7 @@
         <v>0.222075</v>
       </c>
       <c r="AY29" t="n">
-        <v>1659.81813175564</v>
+        <v>1875.44103175564</v>
       </c>
       <c r="AZ29" t="n">
         <v>319.290685298162</v>
